--- a/Assets/@Resources/Data/Excel/ProductData.xlsx
+++ b/Assets/@Resources/Data/Excel/ProductData.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,11 +449,6 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>HpPotion</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
           <t>NameKey</t>
         </is>
       </c>
@@ -491,11 +486,6 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
           <t>string</t>
         </is>
       </c>
@@ -532,11 +522,6 @@
         </is>
       </c>
       <c r="G3" t="inlineStr">
-        <is>
-          <t>회복물약</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
         <is>
           <t>이름 로컬라이즈 키</t>
         </is>
@@ -565,10 +550,7 @@
       <c r="F4" t="n">
         <v>5</v>
       </c>
-      <c r="G4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>ProductStarterText</t>
         </is>
@@ -597,10 +579,7 @@
       <c r="F5" t="n">
         <v>0</v>
       </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>ProductStepUp1Text</t>
         </is>
@@ -629,10 +608,7 @@
       <c r="F6" t="n">
         <v>0</v>
       </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>ProductStepUp2Text</t>
         </is>
@@ -661,10 +637,7 @@
       <c r="F7" t="n">
         <v>0</v>
       </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>ProductStepUp3Text</t>
         </is>
@@ -693,10 +666,7 @@
       <c r="F8" t="n">
         <v>0</v>
       </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>ProductMonthlyText</t>
         </is>
@@ -725,10 +695,7 @@
       <c r="F9" t="n">
         <v>0</v>
       </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>ProductAdFreeText</t>
         </is>
@@ -757,10 +724,7 @@
       <c r="F10" t="n">
         <v>0</v>
       </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>ProductCrystalFormat</t>
         </is>
@@ -789,10 +753,7 @@
       <c r="F11" t="n">
         <v>0</v>
       </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>ProductCrystalFormat</t>
         </is>
@@ -821,10 +782,7 @@
       <c r="F12" t="n">
         <v>0</v>
       </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>ProductCrystalFormat</t>
         </is>
@@ -853,10 +811,7 @@
       <c r="F13" t="n">
         <v>0</v>
       </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>ProductCrystalFormat</t>
         </is>
@@ -885,10 +840,7 @@
       <c r="F14" t="n">
         <v>0</v>
       </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>ProductCrystalFormat</t>
         </is>
@@ -917,10 +869,7 @@
       <c r="F15" t="n">
         <v>0</v>
       </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>ProductCrystalFormat</t>
         </is>

--- a/Assets/@Resources/Data/Excel/ProductData.xlsx
+++ b/Assets/@Resources/Data/Excel/ProductData.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -703,40 +703,40 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>5101</v>
+        <v>5007</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>crystal_60</t>
+          <t>growth_pass</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Crystal</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1100</v>
+        <v>12000</v>
       </c>
       <c r="E10" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>ProductCrystalFormat</t>
+          <t>ProductGrowthPassText</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>5102</v>
+        <v>5101</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>crystal_330</t>
+          <t>crystal_60</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -745,10 +745,10 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>5500</v>
+        <v>1100</v>
       </c>
       <c r="E11" t="n">
-        <v>330</v>
+        <v>60</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -761,11 +761,11 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>5103</v>
+        <v>5102</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>crystal_700</t>
+          <t>crystal_330</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -774,10 +774,10 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11000</v>
+        <v>5500</v>
       </c>
       <c r="E12" t="n">
-        <v>700</v>
+        <v>330</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -790,11 +790,11 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>5104</v>
+        <v>5103</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>crystal_2200</t>
+          <t>crystal_700</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -803,10 +803,10 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>33000</v>
+        <v>11000</v>
       </c>
       <c r="E13" t="n">
-        <v>2200</v>
+        <v>700</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -819,11 +819,11 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>5105</v>
+        <v>5104</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>crystal_3800</t>
+          <t>crystal_2200</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>55000</v>
+        <v>33000</v>
       </c>
       <c r="E14" t="n">
-        <v>3800</v>
+        <v>2200</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -848,28 +848,57 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
+        <v>5105</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>crystal_3800</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>55000</v>
+      </c>
+      <c r="E15" t="n">
+        <v>3800</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ProductCrystalFormat</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
         <v>5106</v>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>crystal_8000</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Crystal</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D16" t="n">
         <v>110000</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E16" t="n">
         <v>8000</v>
       </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="inlineStr">
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="inlineStr">
         <is>
           <t>ProductCrystalFormat</t>
         </is>
